--- a/Assets/LingBoCanteen/Datatables/Excel/Dish_New.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Dish_New.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="120">
   <si>
     <t>#</t>
   </si>
@@ -110,6 +110,9 @@
     <t>4005</t>
   </si>
   <si>
+    <t>Recipe_PumpkinSoup</t>
+  </si>
+  <si>
     <t>蘑菇滑鸡煲</t>
   </si>
   <si>
@@ -119,6 +122,9 @@
     <t>3002,3018</t>
   </si>
   <si>
+    <t>Recipe_ChickenWithMushroom</t>
+  </si>
+  <si>
     <t>柠檬雪葩</t>
   </si>
   <si>
@@ -128,6 +134,9 @@
     <t>3003</t>
   </si>
   <si>
+    <t>Recipe_LemonSorbet</t>
+  </si>
+  <si>
     <t>鱼汤</t>
   </si>
   <si>
@@ -140,6 +149,9 @@
     <t>4001,4004,4006</t>
   </si>
   <si>
+    <t>Recipe_FishSoup</t>
+  </si>
+  <si>
     <t>盐葱香煎牛肉</t>
   </si>
   <si>
@@ -149,6 +161,9 @@
     <t>3004,3007,3017</t>
   </si>
   <si>
+    <t>Recipe_BeefWithScallions</t>
+  </si>
+  <si>
     <t>牛排</t>
   </si>
   <si>
@@ -158,6 +173,9 @@
     <t>3002,3005,3017</t>
   </si>
   <si>
+    <t>Recipe_Steak</t>
+  </si>
+  <si>
     <t>柠檬虾滑</t>
   </si>
   <si>
@@ -170,6 +188,9 @@
     <t>4002,4005</t>
   </si>
   <si>
+    <t>Recipe_LemonShrimpPaste</t>
+  </si>
+  <si>
     <t>仰望星空派</t>
   </si>
   <si>
@@ -182,6 +203,9 @@
     <t>4002</t>
   </si>
   <si>
+    <t>Recipe_StargazyPie</t>
+  </si>
+  <si>
     <t>石板烤肉</t>
   </si>
   <si>
@@ -194,6 +218,9 @@
     <t>4002,4004</t>
   </si>
   <si>
+    <t>Recipe_StoneGrilledMeat</t>
+  </si>
+  <si>
     <t>蒜泥青苹果鸡排</t>
   </si>
   <si>
@@ -206,6 +233,9 @@
     <t>4002,4004,4006</t>
   </si>
   <si>
+    <t>Recipe_AppleChickenCutlet</t>
+  </si>
+  <si>
     <t>青苹果柠檬果冻杯</t>
   </si>
   <si>
@@ -218,6 +248,9 @@
     <t>4003,4005</t>
   </si>
   <si>
+    <t>Recipe_AppleJellyCup</t>
+  </si>
+  <si>
     <t>烤鱼</t>
   </si>
   <si>
@@ -227,6 +260,9 @@
     <t>3003,3006,3007,3019</t>
   </si>
   <si>
+    <t>Recipe_ToastedFish</t>
+  </si>
+  <si>
     <t>番茄肉酱面</t>
   </si>
   <si>
@@ -236,9 +272,15 @@
     <t>2014,3022</t>
   </si>
   <si>
+    <t>Recipe_TomatoMeatNoodles</t>
+  </si>
+  <si>
     <t>番茄肉酱</t>
   </si>
   <si>
+    <t>TamotoMeatSauce</t>
+  </si>
+  <si>
     <t>3004,3012,3020</t>
   </si>
   <si>
@@ -257,6 +299,9 @@
     <t>4004</t>
   </si>
   <si>
+    <t>Recipe_EggFriedRice</t>
+  </si>
+  <si>
     <t>水晶山楂糕</t>
   </si>
   <si>
@@ -266,6 +311,9 @@
     <t>3011,3014</t>
   </si>
   <si>
+    <t>Recipe_HawthornJelly</t>
+  </si>
+  <si>
     <t>牛肉滑蛋饭</t>
   </si>
   <si>
@@ -278,15 +326,21 @@
     <t>4004,4006</t>
   </si>
   <si>
+    <t>Recipe_RiceWithSlicedBeefEggs</t>
+  </si>
+  <si>
     <t>番茄酿肉</t>
   </si>
   <si>
-    <t>Dishes_Tomato StuffedWithMeat</t>
+    <t>Dishes_TomatoStuffedWithMeat</t>
   </si>
   <si>
     <t>‘3002,3004,3012,3020,3023</t>
   </si>
   <si>
+    <t>Recipe_TomatoStuffedWithMeat</t>
+  </si>
+  <si>
     <t>芝士肉酱土豆饼</t>
   </si>
   <si>
@@ -296,6 +350,9 @@
     <t>3008,3015,3017,1023</t>
   </si>
   <si>
+    <t>Recipe_CheesePotatoPancake</t>
+  </si>
+  <si>
     <t>青菜鸡蛋面</t>
   </si>
   <si>
@@ -305,6 +362,9 @@
     <t>‘3007,3016,3022,3023</t>
   </si>
   <si>
+    <t>Recipe_VeggieAndEggNoodles</t>
+  </si>
+  <si>
     <t>沙拉</t>
   </si>
   <si>
@@ -314,6 +374,9 @@
     <t>‘3004,3016,3018,3023,</t>
   </si>
   <si>
+    <t>Recipe_Salad</t>
+  </si>
+  <si>
     <t>小鸡滑蛋盖浇饭</t>
   </si>
   <si>
@@ -321,6 +384,9 @@
   </si>
   <si>
     <t>3008,3010,3013,3015,3017,3023</t>
+  </si>
+  <si>
+    <t>Recipe_Oyakodon</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1345,7 @@
     <col min="5" max="5" width="27.9469026548673" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.0619469026549" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.0088495575221" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.4159292035398" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.4778761061947" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.283185840708" style="1" customWidth="1"/>
     <col min="10" max="10" width="16.929203539823" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.070796460177" customWidth="1"/>
@@ -1411,6 +1477,9 @@
       <c r="G5" s="1">
         <v>5004</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
@@ -1423,19 +1492,22 @@
         <v>2002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1">
         <v>4004</v>
       </c>
       <c r="G6" s="1">
         <v>5003</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -1449,19 +1521,22 @@
         <v>2003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="1">
         <v>5004</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -1475,19 +1550,22 @@
         <v>2004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G8" s="1">
         <v>5004</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="I8" s="1">
         <v>2</v>
@@ -1501,19 +1579,22 @@
         <v>2005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="G9" s="1">
         <v>5001</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -1527,19 +1608,22 @@
         <v>2006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1">
         <v>5001</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="I10" s="1">
         <v>2</v>
@@ -1553,19 +1637,22 @@
         <v>2007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G11" s="1">
         <v>5004</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
@@ -1579,19 +1666,22 @@
         <v>2008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G12" s="1">
         <v>5005</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="I12" s="1">
         <v>3</v>
@@ -1605,19 +1695,22 @@
         <v>2009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G13" s="1">
         <v>5005</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="I13" s="1">
         <v>3</v>
@@ -1631,19 +1724,22 @@
         <v>2010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G14" s="1">
         <v>5001</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="I14" s="1">
         <v>3</v>
@@ -1657,19 +1753,22 @@
         <v>2011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G15" s="1">
         <v>5004</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="I15" s="1">
         <v>4</v>
@@ -1683,19 +1782,22 @@
         <v>2012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" s="1">
         <v>5005</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="I16" s="1">
         <v>4</v>
@@ -1709,16 +1811,19 @@
         <v>2013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G17" s="1">
         <v>5001</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="I17" s="1">
         <v>4</v>
@@ -1732,19 +1837,19 @@
         <v>2014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="G18" s="1">
         <v>5001</v>
-      </c>
-      <c r="I18" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:10">
@@ -1752,19 +1857,22 @@
         <v>2015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="G19" s="1">
         <v>5001</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="I19" s="1">
         <v>5</v>
@@ -1778,19 +1886,22 @@
         <v>2016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="1">
         <v>5002</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="I20" s="1">
         <v>5</v>
@@ -1804,19 +1915,22 @@
         <v>2017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G21" s="1">
         <v>5001</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="I21" s="1">
         <v>5</v>
@@ -1830,19 +1944,22 @@
         <v>2018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G22" s="1">
         <v>5005</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="I22" s="1">
         <v>5</v>
@@ -1856,19 +1973,22 @@
         <v>2019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G23" s="1">
         <v>5001</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="I23" s="1">
         <v>6</v>
@@ -1882,19 +2002,22 @@
         <v>2020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G24" s="1">
         <v>5004</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="I24" s="1">
         <v>6</v>
@@ -1908,19 +2031,22 @@
         <v>2021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G25" s="1">
         <v>5001</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="I25" s="1">
         <v>6</v>
@@ -1934,19 +2060,22 @@
         <v>2022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G26" s="1">
         <v>5004</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="I26" s="1">
         <v>6</v>
